--- a/domain_maintainer/domain_data.xlsx
+++ b/domain_maintainer/domain_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shaked\Documents\GitHub\PQBench\domain_maintainer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shake\Documents\GitHub\PQBench\domain_maintainer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FBAD6B-A64D-4C5A-BAFC-A1B0DB1F011E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F635B074-E322-430A-928C-B4FE19A15207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="video" sheetId="17" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="1372">
   <si>
     <t>https://www.dafont.com/</t>
   </si>
@@ -826,12 +826,6 @@
     <t>play-btn</t>
   </si>
   <si>
-    <t>https://103fm.maariv.co.il/programs/media.aspx?ZrqvnVq=JMKGDJ&amp;c41t4nzVQ=JKF</t>
-  </si>
-  <si>
-    <t>css-18o0txe</t>
-  </si>
-  <si>
     <t>https://www.995.co.il/popup-player</t>
   </si>
   <si>
@@ -3748,9 +3742,6 @@
     <t>phx-ready-play-button-container</t>
   </si>
   <si>
-    <t>https://techcrunch.com/podcast/from-streaming-to-healthcare-to-ai-mark-cuban-reveals-his-disruption-formula/</t>
-  </si>
-  <si>
     <t>https://www.plus.fifa.com/en/player/ba7b97da-9bc0-4df4-82e3-a7e816195608?catalogId=5313167c-d7d7-4d76-a3b8-36284e30e9da&amp;entryPoint=Default</t>
   </si>
   <si>
@@ -3842,237 +3833,6 @@
   </si>
   <si>
     <t>https://www.thebay.com</t>
-  </si>
-  <si>
-    <t>https://www.shoppersdrugmart.ca</t>
-  </si>
-  <si>
-    <t>https://www.laredoute.fr</t>
-  </si>
-  <si>
-    <t>https://www.cdiscount.com</t>
-  </si>
-  <si>
-    <t>https://www.fnac.com</t>
-  </si>
-  <si>
-    <t>https://www.darty.com</t>
-  </si>
-  <si>
-    <t>https://www.leroymerlin.fr</t>
-  </si>
-  <si>
-    <t>https://www.zalando.com</t>
-  </si>
-  <si>
-    <t>https://www.otto.de</t>
-  </si>
-  <si>
-    <t>https://www.aboutyou.de</t>
-  </si>
-  <si>
-    <t>https://www.breuninger.com</t>
-  </si>
-  <si>
-    <t>https://www.sportsdirect.com</t>
-  </si>
-  <si>
-    <t>https://www.jdsports.com</t>
-  </si>
-  <si>
-    <t>https://www.footlocker.com</t>
-  </si>
-  <si>
-    <t>https://www.dsw.com</t>
-  </si>
-  <si>
-    <t>https://www.backcountry.com</t>
-  </si>
-  <si>
-    <t>https://www.moosejaw.com</t>
-  </si>
-  <si>
-    <t>https://www.cabelas.com</t>
-  </si>
-  <si>
-    <t>https://www.basspro.com</t>
-  </si>
-  <si>
-    <t>https://www.scheels.com</t>
-  </si>
-  <si>
-    <t>https://www.patagonia.com</t>
-  </si>
-  <si>
-    <t>https://www.thenorthface.com</t>
-  </si>
-  <si>
-    <t>https://www.columbia.com</t>
-  </si>
-  <si>
-    <t>https://www.timberland.com</t>
-  </si>
-  <si>
-    <t>https://www.newbalance.com</t>
-  </si>
-  <si>
-    <t>https://www.converse.com</t>
-  </si>
-  <si>
-    <t>https://www.vans.com</t>
-  </si>
-  <si>
-    <t>https://www.finishline.com</t>
-  </si>
-  <si>
-    <t>https://www.myntra.com</t>
-  </si>
-  <si>
-    <t>https://www.flipkart.com</t>
-  </si>
-  <si>
-    <t>https://www.reliancedigital.in</t>
-  </si>
-  <si>
-    <t>https://www.croma.com</t>
-  </si>
-  <si>
-    <t>https://www.ajio.com</t>
-  </si>
-  <si>
-    <t>https://www.tatacliq.com</t>
-  </si>
-  <si>
-    <t>https://www.snapdeal.com</t>
-  </si>
-  <si>
-    <t>https://www.bigbasket.com</t>
-  </si>
-  <si>
-    <t>https://www.nykaa.com</t>
-  </si>
-  <si>
-    <t>https://www.mecca.com.au</t>
-  </si>
-  <si>
-    <t>https://www.woolworths.com.au</t>
-  </si>
-  <si>
-    <t>https://www.coles.com.au</t>
-  </si>
-  <si>
-    <t>https://www.harveynorman.com.au</t>
-  </si>
-  <si>
-    <t>https://www.thegoodguys.com.au</t>
-  </si>
-  <si>
-    <t>https://www.jbhifi.com.au</t>
-  </si>
-  <si>
-    <t>https://www.bunnings.com.au</t>
-  </si>
-  <si>
-    <t>https://www.kmart.com.au</t>
-  </si>
-  <si>
-    <t>https://www.myer.com.au</t>
-  </si>
-  <si>
-    <t>https://www.davidjones.com</t>
-  </si>
-  <si>
-    <t>https://www.kathmandu.com.au</t>
-  </si>
-  <si>
-    <t>https://www.elgiganten.se</t>
-  </si>
-  <si>
-    <t>https://www.komplett.no</t>
-  </si>
-  <si>
-    <t>https://www.proshop.dk</t>
-  </si>
-  <si>
-    <t>https://www.elgiganten.dk</t>
-  </si>
-  <si>
-    <t>https://www.power.no</t>
-  </si>
-  <si>
-    <t>https://www.cdon.com</t>
-  </si>
-  <si>
-    <t>https://www.boozt.com</t>
-  </si>
-  <si>
-    <t>https://www.zalora.com</t>
-  </si>
-  <si>
-    <t>https://www.lazada.com</t>
-  </si>
-  <si>
-    <t>https://shopee.sg</t>
-  </si>
-  <si>
-    <t>https://www.tokopedia.com</t>
-  </si>
-  <si>
-    <t>https://www.bukalapak.com</t>
-  </si>
-  <si>
-    <t>https://www.jd.com</t>
-  </si>
-  <si>
-    <t>https://www.tmall.com</t>
-  </si>
-  <si>
-    <t>https://www.suning.com</t>
-  </si>
-  <si>
-    <t>https://www.temu.com</t>
-  </si>
-  <si>
-    <t>https://www.rakuten.co.jp</t>
-  </si>
-  <si>
-    <t>https://www.yodobashi.com</t>
-  </si>
-  <si>
-    <t>https://www.biccamera.com</t>
-  </si>
-  <si>
-    <t>https://zozo.jp</t>
-  </si>
-  <si>
-    <t>https://www.muji.com</t>
-  </si>
-  <si>
-    <t>https://www.nitori-net.jp</t>
-  </si>
-  <si>
-    <t>https://www.noon.com</t>
-  </si>
-  <si>
-    <t>https://www.namshi.com</t>
-  </si>
-  <si>
-    <t>https://www.extra.com</t>
-  </si>
-  <si>
-    <t>https://www.xcite.com</t>
-  </si>
-  <si>
-    <t>https://www.jarir.com</t>
-  </si>
-  <si>
-    <t>https://www.carrefouruae.com</t>
-  </si>
-  <si>
-    <t>https://www.luluhypermarket.com</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.mx</t>
   </si>
   <si>
     <t>https://game.bitplanets.com/#/game</t>
@@ -5031,7 +4791,7 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="29" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -5052,7 +4812,7 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="29" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -5091,7 +4851,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>23</v>
@@ -5104,7 +4864,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>212</v>
@@ -5200,12 +4960,12 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C39" s="29" t="s">
-        <v>1416</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>1412</v>
+        <v>1332</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>47</v>
@@ -5213,7 +4973,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C41" s="29" t="s">
         <v>49</v>
@@ -5233,18 +4993,18 @@
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="6"/>
       <c r="C44" s="29" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="5"/>
       <c r="C45" s="29" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C46" s="29" t="s">
         <v>56</v>
@@ -5252,7 +5012,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C47" s="29" t="s">
-        <v>1351</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
@@ -5265,7 +5025,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C49" s="29" t="s">
-        <v>1354</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -5290,7 +5050,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C54" s="29" t="s">
-        <v>1415</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
@@ -5300,7 +5060,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C56" s="31" t="s">
-        <v>1353</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
@@ -5313,7 +5073,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C58" s="31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
@@ -5323,230 +5083,230 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C60" s="29" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C62" s="29" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C63" s="29" t="s">
-        <v>1413</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C64" s="29" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" s="29" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" s="29" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" s="29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" s="29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="29" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" s="29" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="29" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" s="29" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="29" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="29" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="29" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="29" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" s="29" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" s="29" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C81" s="29" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" s="29" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C83" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C84" s="29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C85" s="29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C86" s="29" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C87" s="29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C88" s="32" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C89" s="32" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C90" s="32" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>1352</v>
+        <v>1272</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C94" s="32" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C97" s="32" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" s="5" t="s">
-        <v>1411</v>
+        <v>1331</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
@@ -5557,125 +5317,125 @@
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" s="5"/>
       <c r="C100" s="32" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C101" s="32" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" s="6" t="s">
-        <v>1355</v>
+        <v>1275</v>
       </c>
       <c r="C102" s="32" t="s">
-        <v>1356</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C103" s="32" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" s="5" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C104" s="31" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C105" s="31" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" s="5" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C106" s="31" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" s="5" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C107" s="31" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" s="32" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" s="6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C109" s="31" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" s="6" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C110" s="31" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C111" s="32" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" s="6" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C112" s="32" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" s="31" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="6" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" s="5"/>
       <c r="C115" s="31" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C116" s="31" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C117" s="31" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C118" s="31" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
@@ -5683,48 +5443,48 @@
         <v>209</v>
       </c>
       <c r="C119" s="32" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" s="6" t="s">
-        <v>1414</v>
+        <v>1334</v>
       </c>
       <c r="C120" s="31" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C121" s="31" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C122" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C124" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C125" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C126" t="s">
-        <v>1348</v>
+        <v>1268</v>
       </c>
     </row>
   </sheetData>
@@ -5809,7 +5569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FC6163-F89F-44E5-90BE-4CFB44CF1FB4}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5830,7 +5590,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>1434</v>
+        <v>1354</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>64</v>
@@ -5838,7 +5598,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>65</v>
@@ -5854,7 +5614,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>68</v>
@@ -5862,15 +5622,15 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>1433</v>
+        <v>1353</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>69</v>
@@ -5881,7 +5641,7 @@
         <v>215</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -5894,7 +5654,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>71</v>
@@ -5902,23 +5662,23 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
-        <v>1425</v>
+        <v>1345</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1424</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>72</v>
@@ -5926,7 +5686,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>73</v>
@@ -6022,7 +5782,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>50</v>
@@ -6063,7 +5823,7 @@
         <v>232</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>1417</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -6103,7 +5863,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B36" s="5" t="s">
-        <v>1427</v>
+        <v>1347</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>21</v>
@@ -6119,10 +5879,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -6219,10 +5979,10 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" s="5" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
@@ -6251,7 +6011,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B55" s="5" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>264</v>
@@ -6259,69 +6019,69 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" s="5" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="C58" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="5"/>
+      <c r="C59" s="20" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B59" s="5" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B60" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C60" s="20" t="s">
         <v>269</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B60" s="5"/>
-      <c r="C60" s="20" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B61" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>271</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C63" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="C62" s="20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B63" s="5" t="s">
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C63" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C64" s="20" t="s">
-        <v>276</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
@@ -6329,7 +6089,7 @@
         <v>277</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>10</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
@@ -6342,7 +6102,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" s="5" t="s">
-        <v>281</v>
+        <v>774</v>
       </c>
       <c r="C67" s="20" t="s">
         <v>280</v>
@@ -6350,45 +6110,45 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B68" s="5" t="s">
-        <v>776</v>
+        <v>282</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B69" s="5" t="s">
-        <v>284</v>
+      <c r="B69" t="s">
+        <v>775</v>
       </c>
       <c r="C69" s="20" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
-        <v>777</v>
-      </c>
+      <c r="B70" s="5"/>
       <c r="C70" s="20" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B71" s="5"/>
+      <c r="B71" s="5" t="s">
+        <v>412</v>
+      </c>
       <c r="C71" s="20" t="s">
-        <v>287</v>
+        <v>776</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B72" s="5" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>778</v>
+        <v>431</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" s="5" t="s">
-        <v>434</v>
+        <v>1338</v>
       </c>
       <c r="C73" s="20" t="s">
         <v>433</v>
@@ -6396,64 +6156,64 @@
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="s">
-        <v>1418</v>
+        <v>435</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B75" s="5" t="s">
-        <v>437</v>
-      </c>
       <c r="C75" s="20" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B76" s="5" t="s">
+        <v>438</v>
+      </c>
       <c r="C76" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B77" s="5" t="s">
-        <v>440</v>
-      </c>
       <c r="C77" s="20" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B78" s="5" t="s">
+        <v>1348</v>
+      </c>
       <c r="C78" s="20" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>442</v>
+      </c>
+      <c r="C79" s="20" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B79" s="5" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C79" s="20" t="s">
-        <v>442</v>
-      </c>
-    </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>444</v>
+      <c r="B80" s="5" t="s">
+        <v>1339</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B81" s="5" t="s">
-        <v>1419</v>
+      <c r="B81" t="s">
+        <v>445</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C82" s="20" t="s">
@@ -6461,7 +6221,7 @@
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B83" s="5" t="s">
+      <c r="B83" t="s">
         <v>449</v>
       </c>
       <c r="C83" s="20" t="s">
@@ -6469,35 +6229,35 @@
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
-        <v>451</v>
+      <c r="B84" s="5" t="s">
+        <v>1341</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>450</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" s="5" t="s">
-        <v>1421</v>
+        <v>779</v>
       </c>
       <c r="C85" s="20" t="s">
-        <v>1420</v>
+        <v>778</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" s="5" t="s">
-        <v>781</v>
+        <v>232</v>
       </c>
       <c r="C86" s="20" t="s">
-        <v>780</v>
+        <v>450</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
-        <v>232</v>
+        <v>452</v>
       </c>
       <c r="C87" s="20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
@@ -6518,86 +6278,86 @@
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
-        <v>458</v>
+        <v>299</v>
       </c>
       <c r="C90" s="20" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B91" s="5" t="s">
-        <v>301</v>
-      </c>
       <c r="C91" s="20" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B92" s="6" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C92" s="20" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B93" s="6" t="s">
+      <c r="C93" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="C93" s="20" t="s">
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>232</v>
+      </c>
+      <c r="C94" s="20" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C94" s="20" t="s">
-        <v>463</v>
-      </c>
-    </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95" t="s">
-        <v>232</v>
+      <c r="B95" s="5" t="s">
+        <v>1346</v>
       </c>
       <c r="C95" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B96" s="5" t="s">
-        <v>1426</v>
+      <c r="B96" t="s">
+        <v>222</v>
       </c>
       <c r="C96" s="20" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B97" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="20" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" t="s">
-        <v>222</v>
-      </c>
-      <c r="C97" s="20" t="s">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C99" s="20" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
-        <v>470</v>
+      <c r="B100" s="6" t="s">
+        <v>783</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>471</v>
+        <v>782</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" s="6" t="s">
-        <v>785</v>
+        <v>232</v>
       </c>
       <c r="C101" s="20" t="s">
         <v>784</v>
@@ -6607,20 +6367,20 @@
       <c r="B102" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C102" s="20" t="s">
+      <c r="C102" s="19" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>787</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B103" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>787</v>
-      </c>
-    </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B104" t="s">
+      <c r="B104" s="6" t="s">
         <v>789</v>
       </c>
       <c r="C104" s="20" t="s">
@@ -6629,7 +6389,7 @@
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" s="6" t="s">
-        <v>791</v>
+        <v>232</v>
       </c>
       <c r="C105" s="20" t="s">
         <v>790</v>
@@ -6637,42 +6397,42 @@
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C106" s="20" t="s">
         <v>792</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" s="6" t="s">
+        <v>793</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>794</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="C108" s="19" t="s">
         <v>795</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" s="6" t="s">
+        <v>797</v>
+      </c>
+      <c r="C109" s="19" t="s">
         <v>798</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>799</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
@@ -6684,19 +6444,19 @@
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="5" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B113" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C113" s="19" t="s">
         <v>803</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="5" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
@@ -6708,24 +6468,24 @@
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B115" s="6" t="s">
-        <v>808</v>
-      </c>
       <c r="C115" s="19" t="s">
         <v>807</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B116" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="C116" s="19" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="6" t="s">
-        <v>239</v>
+        <v>810</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
@@ -6745,21 +6505,21 @@
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B120" s="6" t="s">
+      <c r="C120" s="19" t="s">
         <v>816</v>
       </c>
-      <c r="C120" s="19" t="s">
-        <v>815</v>
-      </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B121" s="6" t="s">
+        <v>818</v>
+      </c>
       <c r="C121" s="19" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122" s="6" t="s">
-        <v>820</v>
+        <v>232</v>
       </c>
       <c r="C122" s="19" t="s">
         <v>819</v>
@@ -6767,9 +6527,9 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C123" s="19" t="s">
+        <v>822</v>
+      </c>
+      <c r="C123" s="20" t="s">
         <v>821</v>
       </c>
     </row>
@@ -6783,23 +6543,10 @@
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B125" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="C125" s="19" t="s">
         <v>826</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B126" s="6" t="s">
-        <v>829</v>
-      </c>
-      <c r="C126" s="19" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C127" t="s">
-        <v>1236</v>
       </c>
     </row>
   </sheetData>
@@ -6808,10 +6555,10 @@
     <hyperlink ref="C44" r:id="rId2" xr:uid="{1102FEC3-A4A2-4B0F-ADE4-3D751ECF38FC}"/>
     <hyperlink ref="C45" r:id="rId3" xr:uid="{C21D3D86-1F2D-4E8D-A7CB-5189D8F456B6}"/>
     <hyperlink ref="C52" r:id="rId4" xr:uid="{6ED252E3-1A5A-463F-B8CA-EE5F62CFF274}"/>
-    <hyperlink ref="C65" r:id="rId5" xr:uid="{DAEC30C9-1203-405A-92E7-934BB88B171E}"/>
-    <hyperlink ref="C63" r:id="rId6" xr:uid="{DC52B000-1FC8-4907-909D-B434FC0591BC}"/>
-    <hyperlink ref="C59" r:id="rId7" xr:uid="{1AD42A18-5C6A-469C-984A-68CA68C03474}"/>
-    <hyperlink ref="C62" r:id="rId8" xr:uid="{A8465678-1427-486F-BEAC-27B7BF15EF20}"/>
+    <hyperlink ref="C64" r:id="rId5" xr:uid="{DAEC30C9-1203-405A-92E7-934BB88B171E}"/>
+    <hyperlink ref="C62" r:id="rId6" xr:uid="{DC52B000-1FC8-4907-909D-B434FC0591BC}"/>
+    <hyperlink ref="C58" r:id="rId7" xr:uid="{1AD42A18-5C6A-469C-984A-68CA68C03474}"/>
+    <hyperlink ref="C61" r:id="rId8" xr:uid="{A8465678-1427-486F-BEAC-27B7BF15EF20}"/>
     <hyperlink ref="C19" r:id="rId9" xr:uid="{6A0FBB2A-F01F-4F12-A2A2-84B3093329DD}"/>
     <hyperlink ref="C7" r:id="rId10" xr:uid="{5646E514-FD80-400A-861F-C88E87997722}"/>
     <hyperlink ref="C37" r:id="rId11" xr:uid="{E815B360-D8AF-4CCE-9CED-F2C672B9729D}"/>
@@ -6819,38 +6566,38 @@
     <hyperlink ref="C46" r:id="rId13" xr:uid="{CFCDD53B-868B-4558-87DA-9621CCBB313F}"/>
     <hyperlink ref="C48" r:id="rId14" xr:uid="{364A8617-AF30-4696-8915-C49811E408BC}"/>
     <hyperlink ref="C50" r:id="rId15" xr:uid="{49F841D7-7E05-4BC4-B96C-B2D651A60799}"/>
-    <hyperlink ref="C55" r:id="rId16" xr:uid="{029DBA7B-42D5-4D7B-ACD0-4722509BC974}"/>
+    <hyperlink ref="C54" r:id="rId16" xr:uid="{029DBA7B-42D5-4D7B-ACD0-4722509BC974}"/>
     <hyperlink ref="C42" r:id="rId17" xr:uid="{D7452DF6-F577-4F68-898F-87018A9F90E3}"/>
-    <hyperlink ref="C60" r:id="rId18" xr:uid="{E57511F6-433E-4C0A-9E55-A6D616B4B542}"/>
-    <hyperlink ref="C69" r:id="rId19" xr:uid="{F24314A8-AEF1-4DC6-9277-5865C1BD746B}"/>
+    <hyperlink ref="C59" r:id="rId18" xr:uid="{E57511F6-433E-4C0A-9E55-A6D616B4B542}"/>
+    <hyperlink ref="C68" r:id="rId19" xr:uid="{F24314A8-AEF1-4DC6-9277-5865C1BD746B}"/>
     <hyperlink ref="C6" r:id="rId20" xr:uid="{7CBFA681-53A7-4415-9AD9-5A76B0ECA64F}"/>
     <hyperlink ref="C3" r:id="rId21" xr:uid="{6951940F-CF46-444F-A19E-35630FA20CBF}"/>
-    <hyperlink ref="C73" r:id="rId22" xr:uid="{0816F2AF-1DB5-458F-AE49-1E5CF7C136A7}"/>
-    <hyperlink ref="C74" r:id="rId23" xr:uid="{7C1ED965-CA06-4770-BA8F-A1BAA7E1F1C8}"/>
-    <hyperlink ref="C75" r:id="rId24" xr:uid="{B7357A0F-B367-49D6-A153-C11478D12DFC}"/>
-    <hyperlink ref="C76" r:id="rId25" xr:uid="{8833F9AC-5CF1-4529-BA8A-58AE8D5300E2}"/>
-    <hyperlink ref="C77" r:id="rId26" xr:uid="{67E7C466-1D00-4304-A1B0-6DFBA9909318}"/>
-    <hyperlink ref="C78" r:id="rId27" xr:uid="{2C919345-D795-4FA4-A0AF-174C18A3D9D5}"/>
-    <hyperlink ref="C79" r:id="rId28" xr:uid="{C7595222-3D25-4D7F-9793-5BE5B14A50F3}"/>
-    <hyperlink ref="C81" r:id="rId29" xr:uid="{156D2818-A7FF-4F98-A043-08F7EB627C21}"/>
-    <hyperlink ref="C83" r:id="rId30" xr:uid="{FC620A9A-E6B3-4822-A0BE-47775E3B1651}"/>
-    <hyperlink ref="C84" r:id="rId31" xr:uid="{D759BFDC-F3B5-434B-B9CB-CC288929EC6B}"/>
-    <hyperlink ref="C87" r:id="rId32" xr:uid="{CC0152F3-AF67-469E-B869-349F80908643}"/>
-    <hyperlink ref="C88" r:id="rId33" location="google_vignette" xr:uid="{E0F5B004-1E01-47EE-AA27-CA8E57F2172D}"/>
-    <hyperlink ref="C89" r:id="rId34" xr:uid="{9F47C724-4114-45F9-9904-FEAE1ABE67FE}"/>
-    <hyperlink ref="C90" r:id="rId35" xr:uid="{CBA09366-16AB-4018-B9D7-AC2454A6A578}"/>
-    <hyperlink ref="C94" r:id="rId36" xr:uid="{EBC2A465-5D4B-4A49-AB3D-D09A34436712}"/>
-    <hyperlink ref="C96" r:id="rId37" xr:uid="{B65C8090-F223-43A9-9012-D7DE4BE44096}"/>
-    <hyperlink ref="C97" r:id="rId38" xr:uid="{A0877A67-3E65-499C-8E33-CB962BC82AA3}"/>
-    <hyperlink ref="C99" r:id="rId39" xr:uid="{EED23262-F3E0-4DDC-8A09-F1AB864808A9}"/>
-    <hyperlink ref="C101" r:id="rId40" xr:uid="{39184F37-1F32-4CC1-A601-50213BE4E568}"/>
-    <hyperlink ref="C102" r:id="rId41" xr:uid="{CC477983-B136-40D9-B748-86E7E8E2A8B2}"/>
-    <hyperlink ref="C104" r:id="rId42" xr:uid="{25559676-2E9B-4BBE-8A3C-B699A0D1350A}"/>
-    <hyperlink ref="C105" r:id="rId43" xr:uid="{8FBF11B2-D8C5-49AF-9F11-17A6DF2D5E0B}"/>
-    <hyperlink ref="C106" r:id="rId44" xr:uid="{1287C059-522D-43F8-ADB4-66764D938356}"/>
-    <hyperlink ref="C124" r:id="rId45" xr:uid="{F4F8C125-F3F2-44D6-9C5E-7C842DE70104}"/>
+    <hyperlink ref="C72" r:id="rId22" xr:uid="{0816F2AF-1DB5-458F-AE49-1E5CF7C136A7}"/>
+    <hyperlink ref="C73" r:id="rId23" xr:uid="{7C1ED965-CA06-4770-BA8F-A1BAA7E1F1C8}"/>
+    <hyperlink ref="C74" r:id="rId24" xr:uid="{B7357A0F-B367-49D6-A153-C11478D12DFC}"/>
+    <hyperlink ref="C75" r:id="rId25" xr:uid="{8833F9AC-5CF1-4529-BA8A-58AE8D5300E2}"/>
+    <hyperlink ref="C76" r:id="rId26" xr:uid="{67E7C466-1D00-4304-A1B0-6DFBA9909318}"/>
+    <hyperlink ref="C77" r:id="rId27" xr:uid="{2C919345-D795-4FA4-A0AF-174C18A3D9D5}"/>
+    <hyperlink ref="C78" r:id="rId28" xr:uid="{C7595222-3D25-4D7F-9793-5BE5B14A50F3}"/>
+    <hyperlink ref="C80" r:id="rId29" xr:uid="{156D2818-A7FF-4F98-A043-08F7EB627C21}"/>
+    <hyperlink ref="C82" r:id="rId30" xr:uid="{FC620A9A-E6B3-4822-A0BE-47775E3B1651}"/>
+    <hyperlink ref="C83" r:id="rId31" xr:uid="{D759BFDC-F3B5-434B-B9CB-CC288929EC6B}"/>
+    <hyperlink ref="C86" r:id="rId32" xr:uid="{CC0152F3-AF67-469E-B869-349F80908643}"/>
+    <hyperlink ref="C87" r:id="rId33" location="google_vignette" xr:uid="{E0F5B004-1E01-47EE-AA27-CA8E57F2172D}"/>
+    <hyperlink ref="C88" r:id="rId34" xr:uid="{9F47C724-4114-45F9-9904-FEAE1ABE67FE}"/>
+    <hyperlink ref="C89" r:id="rId35" xr:uid="{CBA09366-16AB-4018-B9D7-AC2454A6A578}"/>
+    <hyperlink ref="C93" r:id="rId36" xr:uid="{EBC2A465-5D4B-4A49-AB3D-D09A34436712}"/>
+    <hyperlink ref="C95" r:id="rId37" xr:uid="{B65C8090-F223-43A9-9012-D7DE4BE44096}"/>
+    <hyperlink ref="C96" r:id="rId38" xr:uid="{A0877A67-3E65-499C-8E33-CB962BC82AA3}"/>
+    <hyperlink ref="C98" r:id="rId39" xr:uid="{EED23262-F3E0-4DDC-8A09-F1AB864808A9}"/>
+    <hyperlink ref="C100" r:id="rId40" xr:uid="{39184F37-1F32-4CC1-A601-50213BE4E568}"/>
+    <hyperlink ref="C101" r:id="rId41" xr:uid="{CC477983-B136-40D9-B748-86E7E8E2A8B2}"/>
+    <hyperlink ref="C103" r:id="rId42" xr:uid="{25559676-2E9B-4BBE-8A3C-B699A0D1350A}"/>
+    <hyperlink ref="C104" r:id="rId43" xr:uid="{8FBF11B2-D8C5-49AF-9F11-17A6DF2D5E0B}"/>
+    <hyperlink ref="C105" r:id="rId44" xr:uid="{1287C059-522D-43F8-ADB4-66764D938356}"/>
+    <hyperlink ref="C123" r:id="rId45" xr:uid="{F4F8C125-F3F2-44D6-9C5E-7C842DE70104}"/>
     <hyperlink ref="C34" r:id="rId46" xr:uid="{8F6E1B8B-EAB8-4688-986E-F88149D9132D}"/>
-    <hyperlink ref="C85" r:id="rId47" xr:uid="{38C67513-7A53-49FA-816E-BEBEEC35DA84}"/>
+    <hyperlink ref="C84" r:id="rId47" xr:uid="{38C67513-7A53-49FA-816E-BEBEEC35DA84}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId48"/>
@@ -6862,7 +6609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31A2EFD-A127-47E5-B375-5235669A0921}">
-  <dimension ref="A1:C203"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -6878,87 +6625,87 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C2" s="31" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="31" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" s="31" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C5" s="31" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="31" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" s="31" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C8" s="31" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="31" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="31" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" s="31" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C12" s="31" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" s="31" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" s="31" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C15" s="31" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="31" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" s="31" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" s="31" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.3">
@@ -7043,7 +6790,7 @@
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" s="31" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.3">
@@ -7053,7 +6800,7 @@
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" s="31" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
@@ -7098,7 +6845,7 @@
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" s="31" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.3">
@@ -7148,7 +6895,7 @@
     </row>
     <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" s="31" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="57" spans="3:3" x14ac:dyDescent="0.3">
@@ -7158,12 +6905,12 @@
     </row>
     <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" s="31" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" s="31" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="60" spans="3:3" x14ac:dyDescent="0.3">
@@ -7193,7 +6940,7 @@
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" s="31" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.3">
@@ -7283,7 +7030,7 @@
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" s="31" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.3">
@@ -7323,7 +7070,7 @@
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" s="31" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.3">
@@ -7373,7 +7120,7 @@
     </row>
     <row r="101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C101" s="31" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="102" spans="3:3" x14ac:dyDescent="0.3">
@@ -7398,492 +7145,107 @@
     </row>
     <row r="106" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C106" s="31" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="107" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C107" s="31" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="108" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="109" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C109" s="31" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="110" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C110" s="31" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="111" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C111" s="31" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="112" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C112" s="31" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="113" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C113" s="31" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="114" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C114" s="31" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="115" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C115" s="31" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C116" s="31" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C117" s="31" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C118" s="31" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="119" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C119" s="31" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="120" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C120" s="31" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="121" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C121" s="31" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="122" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C122" s="31" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="123" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C123" s="31" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="124" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C124" s="31" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="125" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C125" s="31" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="126" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C126" s="31" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C127" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C128" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C129" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C130" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C131" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C132" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C133" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C134" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C135" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C136" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C137" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C138" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C139" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C140" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C141" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C142" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C143" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C144" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C145" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C146" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C147" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C148" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C149" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C150" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C151" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C152" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C153" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C154" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C155" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C156" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C157" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C158" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C159" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C160" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C161" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C162" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C163" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C164" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C165" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C166" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C167" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C168" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C169" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C170" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C171" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C172" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C173" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C174" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C175" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C176" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C177" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C178" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C179" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C180" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C181" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C182" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C183" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C184" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C185" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C186" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C187" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C188" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C189" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C190" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C191" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C192" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C193" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C194" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C195" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C196" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C197" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C198" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C199" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C200" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C201" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C202" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C203" t="s">
-        <v>1344</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -7937,146 +7299,146 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="23" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>1064</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>1071</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="23" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D20" s="25"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C22" s="23" t="s">
         <v>170</v>
@@ -8086,21 +7448,21 @@
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="23" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="D23" s="24"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="23" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D24" s="25"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="23" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D25" s="24"/>
     </row>
@@ -8113,27 +7475,27 @@
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D27" s="26"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="D28" s="27"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C29" s="23" t="s">
         <v>168</v>
@@ -8143,7 +7505,7 @@
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="7" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>169</v>
@@ -8153,20 +7515,20 @@
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D31" s="27"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="D32" s="27"/>
     </row>
@@ -8174,17 +7536,17 @@
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="23" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D33" s="27"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D34" s="27"/>
     </row>
@@ -8192,7 +7554,7 @@
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="23" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D35" s="27"/>
     </row>
@@ -8200,7 +7562,7 @@
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="23" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="D36" s="27"/>
     </row>
@@ -8208,79 +7570,79 @@
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="23" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="23" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="23" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C41" s="23" t="s">
         <v>1107</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="23" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="23" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
       <c r="C44" s="23" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
       <c r="C45" s="23" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="C46" s="23" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
       <c r="C47" s="23" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -8292,25 +7654,25 @@
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B49" s="7"/>
       <c r="C49" s="23" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="C50" s="23" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="7"/>
       <c r="C51" s="23" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" s="7"/>
       <c r="C52" s="23" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -8324,7 +7686,7 @@
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="23" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -8338,63 +7700,63 @@
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="23" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="23" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="23" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="23" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="23" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="23" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="23" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="23" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="23" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -8408,62 +7770,62 @@
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="23" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="23" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="23" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="23" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="23" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="23" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="23" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="23" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="7" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C74" s="23" t="s">
         <v>174</v>
@@ -8473,56 +7835,56 @@
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="23" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="23" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="23" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="23" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="23" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="23" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="23" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="23" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -8561,260 +7923,260 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="23" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="23" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="23" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="23" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="23" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="23" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="7"/>
       <c r="C95" s="23" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="23" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="23" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="23" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="23" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="23" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="23" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="23" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B103" s="7"/>
       <c r="C103" s="23" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B104" s="7"/>
       <c r="C104" s="23" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B105" s="22" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C105" s="23" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C106" s="23" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B107" s="7"/>
       <c r="C107" s="23" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C108" s="23" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B109" s="7"/>
       <c r="C109" s="23" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="23" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B111" s="7"/>
       <c r="C111" s="23" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
       <c r="C112" s="23" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="7"/>
       <c r="C113" s="23" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C114" s="23" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" s="7"/>
       <c r="C115" s="23" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B116" s="7"/>
       <c r="C116" s="23" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C117" s="23" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" s="7"/>
       <c r="C118" s="23" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B119" s="7"/>
       <c r="C119" s="23" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" s="7"/>
       <c r="C120" s="23" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="7"/>
       <c r="C121" s="23" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122" s="7"/>
       <c r="C122" s="23" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123" s="7"/>
       <c r="C123" s="23" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124" s="7"/>
       <c r="C124" s="23" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B125" s="7"/>
       <c r="C125" s="23" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C126" s="23" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C127" s="23" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="131" spans="3:3" x14ac:dyDescent="0.3">
@@ -8918,45 +8280,45 @@
         <v>202</v>
       </c>
       <c r="D1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
-        <v>1358</v>
+        <v>1278</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>1357</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>1369</v>
+        <v>1289</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>1359</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="7"/>
       <c r="C6" s="13" t="s">
-        <v>1370</v>
+        <v>1290</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="9"/>
@@ -8964,41 +8326,41 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
       <c r="C8" s="35" t="s">
-        <v>1371</v>
+        <v>1291</v>
       </c>
       <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="C10" s="20" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="35" t="s">
-        <v>1374</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>0</v>
@@ -9006,23 +8368,23 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
-        <v>1373</v>
+        <v>1293</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1372</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>1376</v>
+        <v>1296</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>1375</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>1</v>
@@ -9030,270 +8392,270 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="17" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="17" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="C25" s="14" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="7"/>
       <c r="C28" s="33" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
       <c r="C30" s="33" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
-        <v>1378</v>
+        <v>1298</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33" s="17" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>1379</v>
+        <v>1299</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="C35" s="34" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="17" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
       <c r="C38" s="16" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="17" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="7"/>
       <c r="C40" s="34" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
       <c r="C41" s="34" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" s="17" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
       <c r="C44" s="34" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
       <c r="C45" s="14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="17" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
       <c r="C47" s="34" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B48" s="17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B49" s="17" t="s">
-        <v>1380</v>
+        <v>1300</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="17" t="s">
-        <v>1381</v>
+        <v>1301</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -9301,561 +8663,561 @@
         <v>237</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B53" s="17" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B54" s="17" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B55" s="17" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>1382</v>
+        <v>1302</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B57" s="17" t="s">
-        <v>1383</v>
+        <v>1303</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C58" s="16" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B59" s="17" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B61" s="7"/>
       <c r="C61" s="14" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62" s="17" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B63" s="17" t="s">
-        <v>1384</v>
+        <v>1304</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B64" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B65" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B66" s="17" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B68" s="17" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" s="17" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
       <c r="C71" s="34" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B72" s="17" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" s="17" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B74" s="17"/>
       <c r="C74" s="34" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B75" s="17" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B76" s="17" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C77" s="13" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C78" s="13" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B80" s="5" t="s">
-        <v>1385</v>
+        <v>1305</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B82" s="5" t="s">
-        <v>1386</v>
+        <v>1306</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" s="5" t="s">
-        <v>1387</v>
+        <v>1307</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
-        <v>1388</v>
+        <v>1308</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B88" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91" s="5" t="s">
-        <v>1389</v>
+        <v>1309</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B92" s="7"/>
       <c r="C92" s="14" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" s="5" t="s">
-        <v>1390</v>
+        <v>1310</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
-        <v>1391</v>
+        <v>1311</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="s">
-        <v>1392</v>
+        <v>1312</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B96" s="6" t="s">
-        <v>1393</v>
+        <v>1313</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>1360</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97" s="6" t="s">
-        <v>1362</v>
+        <v>1282</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>1361</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C98" s="19" t="s">
-        <v>1363</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" s="6" t="s">
-        <v>1365</v>
+        <v>1285</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>1364</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" s="6" t="s">
-        <v>1394</v>
+        <v>1314</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>1366</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" s="6" t="s">
-        <v>1368</v>
+        <v>1288</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>1367</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" s="5" t="s">
-        <v>1395</v>
+        <v>1315</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>1377</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>1396</v>
+        <v>1316</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105" s="7" t="s">
-        <v>1397</v>
+        <v>1317</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106" s="17" t="s">
-        <v>1398</v>
+        <v>1318</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107" s="17"/>
       <c r="C107" s="13" t="s">
-        <v>1399</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108" s="17"/>
       <c r="C108" s="13" t="s">
-        <v>1400</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>1401</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110" s="6" t="s">
-        <v>1403</v>
+        <v>1323</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>1402</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B111" s="6" t="s">
-        <v>1405</v>
+        <v>1325</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>1404</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112" s="5"/>
       <c r="C112" s="19" t="s">
-        <v>1406</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="6" t="s">
-        <v>1408</v>
+        <v>1328</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>1407</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="6" t="s">
-        <v>1410</v>
+        <v>1330</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>1409</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
-        <v>1436</v>
+        <v>1356</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>1435</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C116" s="1" t="s">
-        <v>1438</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C117" s="1" t="s">
-        <v>1437</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>1440</v>
+        <v>1360</v>
       </c>
       <c r="C118" t="s">
-        <v>1439</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
-        <v>1451</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
-        <v>1442</v>
+        <v>1362</v>
       </c>
       <c r="C120" t="s">
-        <v>1441</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="6" t="s">
-        <v>1444</v>
+        <v>1364</v>
       </c>
       <c r="C121" t="s">
-        <v>1443</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C122" s="6" t="s">
-        <v>1445</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123" s="6" t="s">
-        <v>1365</v>
+        <v>1285</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1446</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C124" t="s">
-        <v>1447</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C125" s="6" t="s">
-        <v>1448</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B126" s="6" t="s">
-        <v>1450</v>
+        <v>1370</v>
       </c>
       <c r="C126" t="s">
-        <v>1449</v>
+        <v>1369</v>
       </c>
     </row>
   </sheetData>
@@ -9965,7 +9327,7 @@
         <v>222</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -9973,7 +9335,7 @@
         <v>232</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -9986,7 +9348,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C5" s="29" t="s">
         <v>186</v>
@@ -9994,7 +9356,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="29" t="s">
-        <v>1346</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -10004,7 +9366,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C8" s="29" t="s">
         <v>188</v>
@@ -10012,7 +9374,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>189</v>
@@ -10020,7 +9382,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>190</v>
@@ -10028,7 +9390,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>191</v>
@@ -10036,36 +9398,36 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C15" s="29" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>193</v>
@@ -10076,12 +9438,12 @@
         <v>222</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>194</v>
@@ -10089,12 +9451,12 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="29" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" s="29" t="s">
-        <v>1345</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -10102,39 +9464,39 @@
         <v>232</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>1349</v>
+        <v>1269</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -10142,42 +9504,42 @@
         <v>232</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C27" s="31" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C28" s="32" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C29" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C30" s="31" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C31" s="32" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C32" s="29" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="32" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
@@ -10187,172 +9549,172 @@
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" s="29" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" s="32" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" s="32" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" s="32" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" s="32" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" s="31" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" s="31" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" s="31" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" s="32" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" s="31" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" s="32" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" s="31" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" s="29" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C48" s="29" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" s="31" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" s="31" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" s="32" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" s="32" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" s="32" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" s="31" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" s="32" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" s="29" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" s="29" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" s="31" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" s="31" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" s="32" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" s="32" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" s="32" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" s="31" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" s="32" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" s="29" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="69" spans="3:3" x14ac:dyDescent="0.3">
@@ -10362,112 +9724,112 @@
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="29" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="29" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" s="32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" s="32" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" s="29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="32" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="29" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" s="32" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" s="32" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" s="29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C82" s="32" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" s="32" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C84" s="29" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C85" s="32" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C86" s="29" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C87" s="29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C88" s="31" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="89" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C89" s="29" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="90" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C90" s="31" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" s="32" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.3">
@@ -10477,62 +9839,62 @@
     </row>
     <row r="93" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C93" s="31" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="94" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C94" s="32" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="95" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C95" s="29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C96" s="29" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C97" s="32" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C98" s="31" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="99" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C99" s="31" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C100" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C101" s="31" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="102" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C102" s="31" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="103" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C103" s="32" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="104" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C104" s="32" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="3:3" x14ac:dyDescent="0.3">
@@ -10542,37 +9904,37 @@
     </row>
     <row r="106" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C106" s="32" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="107" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C107" s="29" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="108" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C108" s="31" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="109" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C109" s="32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="110" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C110" s="29" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C111" s="31" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="112" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C112" s="31" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -10580,12 +9942,12 @@
         <v>232</v>
       </c>
       <c r="C113" s="29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C114" s="29" t="s">
         <v>196</v>
@@ -10598,15 +9960,15 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C116" s="29" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C117" s="29" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -10614,28 +9976,28 @@
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
-        <v>1347</v>
+        <v>1267</v>
       </c>
       <c r="C119" s="29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C120" s="29" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C121" s="29" t="s">
         <v>200</v>
@@ -10643,25 +10005,25 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C122" s="29" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C123" s="29" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C124" s="29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C125" s="29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -10669,10 +10031,10 @@
         <v>50</v>
       </c>
       <c r="B126" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C126" s="29" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -10683,7 +10045,7 @@
         <v>261</v>
       </c>
       <c r="C127" s="29" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -10691,10 +10053,10 @@
         <v>30</v>
       </c>
       <c r="B128" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C128" s="29" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -10817,773 +10179,773 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="17" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="17"/>
       <c r="C3" s="20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" s="19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="20" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" s="19" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="20" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="17" t="s">
-        <v>1432</v>
+        <v>1352</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>1431</v>
+        <v>1351</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C29" s="19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="C32" s="20" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C33" s="20" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="17"/>
       <c r="C34" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C36" s="20" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="17" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="17" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40" s="17" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41" s="7" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C42" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
-        <v>1350</v>
+        <v>1270</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C55" s="19" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" s="17" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C57" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C59" s="19" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C60" s="19" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C61" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C62" s="19" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C63" s="19" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C64" s="20" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C65" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B66" s="7"/>
       <c r="C66" s="19" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B67" s="17" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B68" s="7" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B70" s="7" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B71" s="7" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B72" s="7" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C74" s="19" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B75" s="7" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B76" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B77" s="7" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B78" s="7" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" s="7" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83" s="7" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B84" s="7" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86" s="7" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C88" s="19" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B90" s="7" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C91" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B92" s="7" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B94" s="7" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B96" s="7" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B97" s="7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C98" s="19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B99" s="7"/>
       <c r="C99" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C100" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C101" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C102" s="19" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B103" s="7" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B104" s="7" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C104" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B106" s="7" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C106" s="20" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C107" s="20" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B108" s="7" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C108" s="19" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -11591,140 +10953,140 @@
         <v>237</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B110" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C110" s="20" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B111" s="5" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B112" s="5" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115" s="6" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B116" s="6" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117" s="5" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B119" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120" s="6" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122" s="6" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C122" s="19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C123" s="20" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124" s="6" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B125" s="6" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C126" s="20" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -11780,690 +11142,690 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C29" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C31" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="5"/>
       <c r="C32" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C33" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C34" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C35" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36" s="5" t="s">
-        <v>1430</v>
+        <v>1350</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C37" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C39" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C41" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C43" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C45" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C47" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C48" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C49" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C52" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C53" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B54" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C55" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C56" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C57" s="1" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>1429</v>
+        <v>1349</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C63" s="1" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C65" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C69" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B70" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C71" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C72" s="1" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C73" s="1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C74" s="1" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C75" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C77" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C78" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C79" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C81" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C82" s="1" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C83" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C85" s="1" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C86" s="1" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C87" s="1" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C88" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C89" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C90" s="1" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C91" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C93" s="1" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C94" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C95" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C97" s="1" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C99" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C100" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102" s="6" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C105" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C106" s="1" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C108" s="1" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C109" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C110" s="1" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C111" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C114" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C116" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C117" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C119" s="1" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C120" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C121" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C122" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C123" s="1" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C124" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C125" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C126" s="1" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
